--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1730-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1730-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00E7BAF5-BE4F-4B58-8F78-57FD97A2647E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81673174-8835-4859-A083-C8642214AF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{59DD557E-77E1-4562-9959-656EC27FAFE9}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{307E06C6-5A7D-482E-B735-842CCE07140B}"/>
   </bookViews>
   <sheets>
     <sheet name="1730-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1526,30 +1526,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71A6994-2743-475F-993E-A1A6A0025E1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A85120-5ACF-4D45-8479-21DA1F173BA5}">
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1739,7 +1739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2021</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2020</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2019</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2018</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2016</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2015</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2014</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2013</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2012</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2011</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2010</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2009</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2008</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2007</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2006</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2005</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2004</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2003</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2002</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2001</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2000</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>1999</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1998</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>1997</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
         <v>63</v>
       </c>
